--- a/用卷/xlsx/常规科目/2001.xlsx
+++ b/用卷/xlsx/常规科目/2001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0D9F0F-72F7-4F57-950E-E1CAD8CDCA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F105BF-0DF7-4DCB-A375-3A817EDD9D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -538,6 +538,26 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>豫粤卷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t>,上海卷</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -572,6 +592,26 @@
         <charset val="134"/>
       </rPr>
       <t>旧课程理综卷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>豫粤卷</t>
     </r>
     <r>
       <rPr>
@@ -776,9 +816,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -799,6 +836,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1085,11 +1125,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1257,7 +1297,7 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="23" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="19" t="s">
@@ -1271,7 +1311,7 @@
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="25"/>
+      <c r="C15" s="24"/>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1556,11 +1596,11 @@
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -1615,10 +1655,10 @@
       <c r="A44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="22">
-        <v>6</v>
-      </c>
-      <c r="C44" s="20" t="s">
+      <c r="B44" s="21">
+        <v>7</v>
+      </c>
+      <c r="C44" s="27" t="s">
         <v>70</v>
       </c>
       <c r="D44" s="8"/>
@@ -1627,8 +1667,8 @@
       <c r="A45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="21"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="8"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1636,9 +1676,9 @@
         <v>37</v>
       </c>
       <c r="B46" s="4">
-        <v>3</v>
-      </c>
-      <c r="C46" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D46" s="8"/>
@@ -1647,10 +1687,10 @@
       <c r="A47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="22">
-        <v>6</v>
-      </c>
-      <c r="C47" s="20" t="s">
+      <c r="B47" s="21">
+        <v>7</v>
+      </c>
+      <c r="C47" s="27" t="s">
         <v>70</v>
       </c>
       <c r="D47" s="8"/>
@@ -1659,8 +1699,8 @@
       <c r="A48" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="21"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -1668,9 +1708,9 @@
         <v>40</v>
       </c>
       <c r="B49" s="4">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D49" s="8"/>
